--- a/veterinarian_forms/037_animal_transfer_form--veterinarian_forms.xlsx
+++ b/veterinarian_forms/037_animal_transfer_form--veterinarian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,11 +528,7 @@
           <t>Date of Transfer</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Date animal is being transferred</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -547,19 +543,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>section_transferring_party</t>
+          <t>transferring_party_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-- Transferring Party Information --</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Current owner or caretaker</t>
-        </is>
-      </c>
+          <t>Transferring Party Information</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -574,19 +566,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>transferring_party_name</t>
+          <t>transferring_party_name_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Your full name</t>
-        </is>
-      </c>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -609,11 +597,7 @@
           <t>Address</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Street address</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -636,11 +620,7 @@
           <t>City</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -663,11 +643,7 @@
           <t>State</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>State or province</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -690,11 +666,7 @@
           <t>Phone Number</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Contact phone</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -717,11 +689,7 @@
           <t>Email Address</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Contact email</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -736,19 +704,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>section_receiving_party</t>
+          <t>receiving_party_name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-- Receiving Party Information --</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>New owner or caretaker</t>
-        </is>
-      </c>
+          <t>Receiving Party Information</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -763,19 +727,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>receiving_party_name</t>
+          <t>receiving_party_name_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Full name of receiving party</t>
-        </is>
-      </c>
+          <t>Receiving Party Name 2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -795,14 +755,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Street address</t>
-        </is>
-      </c>
+          <t>Receiving Party Address</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -822,14 +778,10 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
+          <t>Receiving Party City</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -849,14 +801,10 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>State or province</t>
-        </is>
-      </c>
+          <t>Receiving Party State</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>yes</t>
@@ -876,14 +824,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Contact phone</t>
-        </is>
-      </c>
+          <t>Receiving Party Phone</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>yes</t>
@@ -903,14 +847,10 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Email Address</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Contact email</t>
-        </is>
-      </c>
+          <t>Receiving Party Email</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -920,51 +860,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>section_animal_info</t>
+          <t>animal_name</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-- Animal Information --</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Details about the animal</t>
-        </is>
-      </c>
+          <t>Animal Name</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>animal_name</t>
+          <t>animal_species</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Animal Name</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Pet's name</t>
-        </is>
-      </c>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>yes</t>
@@ -974,27 +906,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>animal_species</t>
+          <t>animal_breed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Type of animal</t>
-        </is>
-      </c>
+          <t>Breed</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1006,46 +934,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>animal_breed</t>
+          <t>animal_age</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Breed</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Breed or mix</t>
-        </is>
-      </c>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>animal_age</t>
+          <t>animal_gender</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Age of animal</t>
-        </is>
-      </c>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1055,27 +975,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>animal_gender</t>
+          <t>animal_color</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Male or female</t>
-        </is>
-      </c>
+          <t>Color or Markings</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1087,19 +1003,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>animal_color</t>
+          <t>animal_weight</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Color or Markings</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Physical description</t>
-        </is>
-      </c>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>no</t>
@@ -1114,19 +1026,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>animal_weight</t>
+          <t>animal_microchip</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Weight in pounds or kilograms</t>
-        </is>
-      </c>
+          <t>Microchip Number</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
@@ -1136,24 +1044,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>animal_microchip</t>
+          <t>section_medical_history</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Microchip Number</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Identification number if applicable</t>
-        </is>
-      </c>
+          <t>Medical History</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
@@ -1168,19 +1072,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>animal_photo</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Photo or Identifying Features</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Description of identifying features</t>
-        </is>
-      </c>
+          <t>Known Medical Conditions</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
@@ -1190,24 +1090,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>section_medical_history</t>
+          <t>current_medications</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-- Medical History --</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Health information about animal</t>
-        </is>
-      </c>
+          <t>Current Medications</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
@@ -1222,19 +1118,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Known Medical Conditions</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Any health issues</t>
-        </is>
-      </c>
+          <t>Allergies or Dietary Restrictions</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>no</t>
@@ -1244,27 +1136,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>current_medications</t>
+          <t>transfer_reason</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Current Medications</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Medications being taken</t>
-        </is>
-      </c>
+          <t>Reason for Transfer</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1276,19 +1164,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>transfer_reason_details</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Allergies or Dietary Restrictions</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Any known allergies</t>
-        </is>
-      </c>
+          <t>Additional Details</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>no</t>
@@ -1298,24 +1182,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>vaccination_status</t>
+          <t>section_behavioral_info</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vaccination Status</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Current vaccination status</t>
-        </is>
-      </c>
+          <t>Behavioral Information</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>no</t>
@@ -1325,27 +1205,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>spay_neuter</t>
+          <t>behavioral_notes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spay or Neuter Status</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Whether animal has been spayed or neutered</t>
-        </is>
-      </c>
+          <t>Behavioral Notes</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1357,19 +1233,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>veterinarian_name</t>
+          <t>known_issues</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Current Veterinarian Name</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Name of vet</t>
-        </is>
-      </c>
+          <t>Known Issues</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>no</t>
@@ -1384,19 +1256,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>veterinarian_contact</t>
+          <t>special_care_needs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Veterinarian Contact Information</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Phone or email</t>
-        </is>
-      </c>
+          <t>Special Care or Training Needs</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>no</t>
@@ -1411,19 +1279,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>section_behavior</t>
+          <t>section_acknowledgment</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-- Behavioral Information --</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Behavioral characteristics</t>
-        </is>
-      </c>
+          <t>Acknowledgment and Agreement</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>no</t>
@@ -1433,295 +1297,90 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>behavioral_notes</t>
+          <t>acknowledge_receipt</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Behavioral Notes</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Temperament and personality</t>
-        </is>
-      </c>
+          <t>Receiving Party Acknowledges Receipt</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>known_issues</t>
+          <t>acknowledge_condition</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Known Behavioral or Medical Issues</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Any concerns</t>
-        </is>
-      </c>
+          <t>Receiving Party Acknowledges Condition</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>special_care_needs</t>
+          <t>release_transferring_party</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Special Care or Training Needs</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Specific requirements</t>
-        </is>
-      </c>
+          <t>Transferring Party Released from Liability</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>section_transfer_reason</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-- Reason for Transfer --</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Why animal is being transferred</t>
-        </is>
-      </c>
+          <t>Additional Notes</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>transfer_reason</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Reason for Transfer</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Explanation</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>transfer_reason_details</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Additional Details</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>More information about reason</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>section_acknowledgment</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>-- Acknowledgment and Agreement --</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Confirmation of transfer</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>acknowledge_receipt</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Receiving Party Acknowledges Receipt</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Confirm receipt of animal</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>acknowledge_condition</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Receiving Party Acknowledges Condition</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Accept animal in current condition</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>release_transferring_party</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Transferring Party Released from Liability</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Confirm release of responsibility</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>additional_notes</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Additional Notes</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Any other relevant information</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1738,7 +1397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1936,51 +1595,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>spay_neuter_choices</t>
+          <t>transfer_reason_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>adoption</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Adoption</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>spay_neuter_choices</t>
+          <t>transfer_reason_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rescue_transfer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Rescue Transfer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>spay_neuter_choices</t>
+          <t>transfer_reason_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>sanctuary_placement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sanctuary Placement</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1651,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>adoption</t>
+          <t>breeding_program</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Adoption</t>
+          <t>Breeding Program</t>
         </is>
       </c>
     </row>
@@ -2009,12 +1668,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rescue_transfer</t>
+          <t>relocation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rescue Transfer</t>
+          <t>Relocation</t>
         </is>
       </c>
     </row>
@@ -2026,12 +1685,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sanctuary_placement</t>
+          <t>end_of_life_care</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sanctuary Placement</t>
+          <t>End of Life Care</t>
         </is>
       </c>
     </row>
@@ -2043,165 +1702,114 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>breeding_program</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Breeding Program</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>transfer_reason_choices</t>
+          <t>acknowledge_receipt_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>relocation</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Relocation</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>transfer_reason_choices</t>
+          <t>acknowledge_receipt_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>end_of_life_care</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>End of Life Care</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>transfer_reason_choices</t>
+          <t>acknowledge_condition_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>acknowledge_receipt_choices</t>
+          <t>acknowledge_condition_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>acknowledge_receipt_choices</t>
+          <t>release_transferring_party_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>acknowledge_condition_choices</t>
+          <t>release_transferring_party_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>acknowledge_condition_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>release_transferring_party_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>release_transferring_party_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
